--- a/research/sd_ground_truth/streetview-batch1.xlsx
+++ b/research/sd_ground_truth/streetview-batch1.xlsx
@@ -802,17 +802,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Avenida Encinas</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>Ponto Road</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Avenida Encinas</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>436431493</t>
+          <t>908227119</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -830,12 +830,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.091805,-117.314255&amp;heading=161</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.092685,-117.314142&amp;heading=342</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.091805,-117.314255</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.092685,-117.314142</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>sources disagree: map uses the official 50 mph (OSM/imagery: osm 30, mapillary 50)</t>
         </is>
       </c>
       <c r="Y4" t="n">
@@ -882,7 +882,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>195</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>908227120</t>
+          <t>33749367</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -932,12 +932,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.093700,-117.314556&amp;heading=340</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.096467,-117.315979&amp;heading=337</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.093700,-117.314556</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.096467,-117.315979</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -976,7 +976,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 50 mph (OSM/imagery: osm 30)</t>
+          <t>sources disagree: map uses the official 50 mph (OSM/imagery: osm 30, mapillary 50)</t>
         </is>
       </c>
       <c r="Y5" t="n">
@@ -984,7 +984,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>474</t>
         </is>
       </c>
     </row>
@@ -1108,17 +1108,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>Ponto Road</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>Poinsettia Lane</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ponto Road</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>436431492</t>
+          <t>435654183</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.098481,-117.316962&amp;heading=166</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.100764,-117.317648&amp;heading=341</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.098481,-117.316962</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.100764,-117.317648</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>sources disagree: map uses the official 50 mph (OSM/imagery: osm 30)</t>
         </is>
       </c>
       <c r="Y7" t="n">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>322</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>435654183</t>
+          <t>435654179</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.100764,-117.317648&amp;heading=341</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.101712,-117.318044&amp;heading=341</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.100764,-117.317648</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.101712,-117.318044</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>63</t>
         </is>
       </c>
     </row>
@@ -1312,17 +1312,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ponto Road</t>
+          <t>Poinsettia Lane</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Poinsettia Lane</t>
+          <t>Breakwater Road</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>436609337</t>
+          <t>435654184</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.101239,-117.317854&amp;heading=341</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.101890,-117.318118&amp;heading=340</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.101239,-117.317854</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.101890,-117.318118</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 50 mph (OSM/imagery: osm 30)</t>
+          <t>sources disagree: map uses the official 50 mph (OSM/imagery: osm 30, mapillary 50)</t>
         </is>
       </c>
       <c r="Y9" t="n">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>409</t>
         </is>
       </c>
     </row>
@@ -1414,17 +1414,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ponto Road</t>
+          <t>Poinsettia Lane</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Poinsettia Lane</t>
+          <t>Breakwater Road</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>435654179</t>
+          <t>435654178</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1442,12 +1442,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.101712,-117.318044&amp;heading=341</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.105886,-117.319926&amp;heading=337</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.101712,-117.318044</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.105886,-117.319926</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>89</t>
         </is>
       </c>
     </row>
@@ -1521,12 +1521,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Poinsettia Lane</t>
+          <t>Island Way</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>435654177</t>
+          <t>436609338</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.102103,-117.318378&amp;heading=160</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.106389,-117.320184&amp;heading=337</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.102103,-117.318378</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.106389,-117.320184</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>sources disagree: map uses the official 50 mph (OSM/imagery: osm 30)</t>
         </is>
       </c>
       <c r="Y11" t="n">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>108</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -1618,17 +1618,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Poinsettia Lane</t>
+          <t>Breakwater Road</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Breakwater Road</t>
+          <t>Island Way</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>435654178</t>
+          <t>436609340</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.105886,-117.319926&amp;heading=337</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.107633,-117.320717&amp;heading=341</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.105886,-117.319926</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.107633,-117.320717</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>106</t>
         </is>
       </c>
     </row>
@@ -1720,17 +1720,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>Breakwater Road</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>Island Way</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Breakwater Road</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>435654180</t>
+          <t>33749309</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.106054,-117.320209&amp;heading=154</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.109272,-117.321377&amp;heading=342</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.106054,-117.320209</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.109272,-117.321377</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>sources disagree: map uses the official 50 mph (OSM/imagery: osm 30, mapillary 50)</t>
         </is>
       </c>
       <c r="Y13" t="n">
@@ -1800,7 +1800,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>469</t>
         </is>
       </c>
     </row>
@@ -1822,21 +1822,21 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Breakwater Road</t>
+          <t>Tierra del Oro</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Island Way</t>
+          <t>Cannon Road</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>436609338</t>
+          <t>436431232</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1845,17 +1845,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.106389,-117.320184&amp;heading=337</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.132611,-117.335539&amp;heading=149</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.106389,-117.320184</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.132611,-117.335539</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1871,12 +1871,12 @@
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (Island Way - south city limit (Batiquitos Lagoon to Leucadia))</t>
+          <t>Carlsbad Blvd (Tamarack - 1,400 ft S of Manzano Dr)</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 50 mph (OSM/imagery: osm 30)</t>
+          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
         </is>
       </c>
       <c r="Y14" t="n">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -1924,21 +1924,21 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Breakwater Road</t>
+          <t>Sequoia Avenue</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Island Way</t>
+          <t>Tierra del Oro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>436609340</t>
+          <t>436431234</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1947,17 +1947,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.107633,-117.320717&amp;heading=341</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.133358,-117.336067&amp;heading=150</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.107633,-117.320717</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.133358,-117.336067</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1973,12 +1973,12 @@
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (Island Way - south city limit (Batiquitos Lagoon to Leucadia))</t>
+          <t>Carlsbad Blvd (Tamarack - 1,400 ft S of Manzano Dr)</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 50 mph (OSM/imagery: osm 30)</t>
+          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30, mapillary 35)</t>
         </is>
       </c>
       <c r="Y15" t="n">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>66</t>
         </is>
       </c>
     </row>
@@ -2026,21 +2026,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Solamar Dr</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Island Way</t>
-        </is>
-      </c>
+          <t>Sequoia Avenue</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>435654181</t>
+          <t>157272815</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2049,17 +2045,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.111770,-117.322672&amp;heading=154</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.144967,-117.343162&amp;heading=143</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.111770,-117.322672</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.144967,-117.343162</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2075,12 +2071,12 @@
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (Island Way - south city limit (Batiquitos Lagoon to Leucadia))</t>
+          <t>Carlsbad Blvd (Tamarack - 1,400 ft S of Manzano Dr)</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2098,7 +2094,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30, mapillary 35)</t>
         </is>
       </c>
       <c r="Y16" t="n">
@@ -2106,7 +2102,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -2128,17 +2124,13 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Solamar Dr</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Island Way</t>
-        </is>
-      </c>
+          <t>Sequoia Avenue</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>437777329</t>
+          <t>157272817</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2151,17 +2143,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.112719,-117.323251&amp;heading=151</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.145299,-117.343467&amp;heading=142</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.112719,-117.323251</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.145299,-117.343467</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2200,7 +2192,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
         </is>
       </c>
       <c r="Y17" t="n">
@@ -2208,7 +2200,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>77</t>
         </is>
       </c>
     </row>
@@ -2230,17 +2222,13 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Tierra del Oro</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Cannon Road</t>
-        </is>
-      </c>
+          <t>Sequoia Avenue</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>436431232</t>
+          <t>404648983</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2258,12 +2246,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.132611,-117.335539&amp;heading=149</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.146294,-117.344337&amp;heading=144</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.132611,-117.335539</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.146294,-117.344337</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2302,7 +2290,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
+          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30, mapillary 35)</t>
         </is>
       </c>
       <c r="Y18" t="n">
@@ -2310,7 +2298,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -2332,17 +2320,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Tierra del Oro</t>
+          <t>Tamarack Avenue</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Cannon Road</t>
+          <t>Sequoia Avenue</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>436431224</t>
+          <t>436429085</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2360,12 +2348,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.132970,-117.335792&amp;heading=149</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.146853,-117.344830&amp;heading=147</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.132970,-117.335792</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.146853,-117.344830</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2412,7 +2400,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -2434,21 +2422,21 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tierra del Oro</t>
+          <t>Beech Avenue</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cannon Road</t>
+          <t>Christiansen Avenue</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>436431226</t>
+          <t>436405051</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2462,12 +2450,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.133216,-117.335966&amp;heading=149</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.160241,-117.352725&amp;heading=145</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.133216,-117.335966</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.160241,-117.352725</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -2483,12 +2471,12 @@
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (Tamarack - 1,400 ft S of Manzano Dr)</t>
+          <t>Carlsbad Blvd (State St - Tamarack Ave)</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2506,7 +2494,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
+          <t>sources disagree: map uses the official 30 mph (OSM/imagery: osm 20)</t>
         </is>
       </c>
       <c r="Y20" t="n">
@@ -2514,7 +2502,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>122</t>
         </is>
       </c>
     </row>
@@ -2536,21 +2524,21 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sequoia Avenue</t>
+          <t>Mountain View Drive</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tierra del Oro</t>
+          <t>Cypress Avenue</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>436431223</t>
+          <t>1085300499</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2564,12 +2552,12 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.133883,-117.336434&amp;heading=150</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.162771,-117.354398&amp;heading=171</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.133883,-117.336434</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.162771,-117.354398</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -2585,12 +2573,12 @@
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (Tamarack - 1,400 ft S of Manzano Dr)</t>
+          <t>Carlsbad Blvd (State St - Tamarack Ave)</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2608,7 +2596,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
+          <t>sources disagree: map uses the official 30 mph (OSM/imagery: mapillary 25)</t>
         </is>
       </c>
       <c r="Y21" t="n">
@@ -2616,7 +2604,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>135</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2626,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sequoia Avenue</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tierra del Oro</t>
+          <t>Mountain View Drive</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>436431236</t>
+          <t>382185424</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -2666,12 +2654,12 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.134116,-117.336598&amp;heading=150</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.166139,-117.354677&amp;heading=155</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.134116,-117.336598</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.166139,-117.354677</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -2692,7 +2680,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (Tamarack - 1,400 ft S of Manzano Dr)</t>
+          <t>Carlsbad Blvd (North city limit - State St)</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2710,7 +2698,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
+          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 15)</t>
         </is>
       </c>
       <c r="Y22" t="n">
@@ -2718,7 +2706,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -2740,17 +2728,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sequoia Avenue</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tamarack Avenue</t>
+          <t>Mountain View Drive</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>436429114</t>
+          <t>407600254</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -2768,12 +2756,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.141602,-117.340718&amp;heading=154</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.166569,-117.354912&amp;heading=145</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.141602,-117.340718</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.166569,-117.354912</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -2794,7 +2782,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (Tamarack - 1,400 ft S of Manzano Dr)</t>
+          <t>Carlsbad Blvd (North city limit - State St)</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2812,7 +2800,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 25)</t>
         </is>
       </c>
       <c r="Y23" t="n">
@@ -2820,7 +2808,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>397</t>
+          <t>211</t>
         </is>
       </c>
     </row>
@@ -2837,22 +2825,26 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Carlsbad Boulevard</t>
+          <t>La Costa Avenue</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sequoia Avenue</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>North Coast Highway</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>North Vulcan Avenue</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>157272817</t>
+          <t>750625054</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2866,12 +2858,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.145299,-117.343467&amp;heading=142</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.082615,-117.308638&amp;heading=50</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.145299,-117.343467</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.082615,-117.308638</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -2887,17 +2879,17 @@
       <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (Tamarack - 1,400 ft S of Manzano Dr)</t>
+          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): La Costa Ave (N Coast Hwy 101 - East City Limits) posted 30</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>https://ecode360.com/44006773</t>
+          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
         </is>
       </c>
       <c r="V24">
@@ -2910,7 +2902,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 30 mph (OSM/imagery: osm 40)</t>
         </is>
       </c>
       <c r="Y24" t="n">
@@ -2918,62 +2910,62 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>38</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CBD-B1-024</t>
+          <t>COR-B1-001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Coronado</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Carlsbad Boulevard</t>
+          <t>3rd Street</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tamarack Avenue</t>
+          <t>C Avenue</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sequoia Avenue</t>
+          <t>Orange Avenue</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>436429085</t>
+          <t>1033773080</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.146853,-117.344830&amp;heading=147</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.695838,-117.173833&amp;heading=296</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.146853,-117.344830</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.695838,-117.173833</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2987,21 +2979,9 @@
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Carlsbad Blvd (Tamarack - 1,400 ft S of Manzano Dr)</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>https://ecode360.com/44006773</t>
-        </is>
-      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
       <c r="V25">
         <f>IF(OR(L25="",S25=""),"",IF(VALUE(L25)=VALUE(S25),"Y","N"))</f>
         <v/>
@@ -3012,7 +2992,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 30, mapillary 25); map shows 25</t>
         </is>
       </c>
       <c r="Y25" t="n">
@@ -3020,39 +3000,39 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>58</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CBD-B1-025</t>
+          <t>COR-B1-002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Coronado</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Carlsbad Boulevard</t>
+          <t>Orange Avenue</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tamarack Avenue</t>
+          <t>Churchill Place</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sequoia Avenue</t>
+          <t>Adella Avenue</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>436429075</t>
+          <t>436413513</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3060,7 +3040,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3070,12 +3050,12 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.147125,-117.345040&amp;heading=146</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.682492,-117.178401&amp;heading=145</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.147125,-117.345040</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.682492,-117.178401</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -3089,21 +3069,9 @@
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Carlsbad Blvd (Tamarack - 1,400 ft S of Manzano Dr)</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>https://ecode360.com/44006773</t>
-        </is>
-      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
       <c r="V26">
         <f>IF(OR(L26="",S26=""),"",IF(VALUE(L26)=VALUE(S26),"Y","N"))</f>
         <v/>
@@ -3114,7 +3082,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
+          <t>sources disagree: sources disagree (osm 30, streetview 35); map shows 35</t>
         </is>
       </c>
       <c r="Y26" t="n">
@@ -3122,39 +3090,39 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>68</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CBD-B1-026</t>
+          <t>COR-B1-003</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Coronado</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Carlsbad Boulevard</t>
+          <t>Orange Avenue</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tamarack Avenue</t>
+          <t>Isabella Avenue</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sequoia Avenue</t>
+          <t>Adella Avenue</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>157272814</t>
+          <t>153343706</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3162,7 +3130,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3172,12 +3140,12 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.147258,-117.345147&amp;heading=146</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.684222,-117.179156&amp;heading=137</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.147258,-117.345147</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.684222,-117.179156</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -3191,21 +3159,9 @@
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Carlsbad Blvd (Tamarack - 1,400 ft S of Manzano Dr)</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>https://ecode360.com/44006773</t>
-        </is>
-      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
       <c r="V27">
         <f>IF(OR(L27="",S27=""),"",IF(VALUE(L27)=VALUE(S27),"Y","N"))</f>
         <v/>
@@ -3216,7 +3172,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
+          <t>sources disagree: sources disagree (osm 30, streetview 35); map shows 35</t>
         </is>
       </c>
       <c r="Y27" t="n">
@@ -3224,43 +3180,43 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>355</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CBD-B1-027</t>
+          <t>DMR-B1-001</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Del Mar</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Carlsbad Boulevard</t>
+          <t>Camino del Mar</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tamarack Avenue</t>
+          <t>27th Street</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Redwood Avenue</t>
+          <t>Sandy Pointe</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>436429102</t>
+          <t>1342043490</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -3269,17 +3225,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.147619,-117.345436&amp;heading=327</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.971681,-117.268312&amp;heading=351</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.147619,-117.345436</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.971681,-117.268312</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -3295,17 +3251,17 @@
       <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (Tamarack - 1,400 ft S of Manzano Dr)</t>
+          <t>Camino del Mar (San Dieguito Bridge - Coast Blvd: posted 25 (survey seg 3))</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>https://ecode360.com/44006773</t>
+          <t>https://www.delmar.ca.us/AgendaCenter/ViewFile/Agenda/_09142026-3926</t>
         </is>
       </c>
       <c r="V28">
@@ -3318,7 +3274,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: mapillary 30)</t>
         </is>
       </c>
       <c r="Y28" t="n">
@@ -3326,43 +3282,43 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>127</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CBD-B1-028</t>
+          <t>DMR-B1-002</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Del Mar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Carlsbad Boulevard</t>
+          <t>Camino del Mar</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Oak Avenue</t>
+          <t>Border Avenue</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pine Avenue</t>
+          <t>Sandy Lane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>436429115</t>
+          <t>436313318</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3371,17 +3327,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.155858,-117.350905&amp;heading=186</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.974201,-117.268885&amp;heading=172</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.155858,-117.350905</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.974201,-117.268885</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -3397,17 +3353,17 @@
       <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (State St - Tamarack Ave)</t>
+          <t>Camino del Mar (San Dieguito Bridge - Coast Blvd: posted 25 (survey seg 3))</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>https://ecode360.com/44006773</t>
+          <t>https://www.delmar.ca.us/AgendaCenter/ViewFile/Agenda/_09142026-3926</t>
         </is>
       </c>
       <c r="V29">
@@ -3420,7 +3376,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 45, mapillary 30)</t>
         </is>
       </c>
       <c r="Y29" t="n">
@@ -3428,43 +3384,43 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>99</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CBD-B1-029</t>
+          <t>DMR-B1-003</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Del Mar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Carlsbad Boulevard</t>
+          <t>Camino del Mar</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Beech Avenue</t>
+          <t>Border Avenue</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Christiansen Avenue</t>
+          <t>Sandy Lane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>436405051</t>
+          <t>157531201</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3473,17 +3429,17 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.160241,-117.352725&amp;heading=145</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.974297,-117.268900&amp;heading=172</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.160241,-117.352725</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.974297,-117.268900</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -3499,17 +3455,17 @@
       <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (State St - Tamarack Ave)</t>
+          <t>Camino del Mar (San Dieguito Bridge - Coast Blvd: posted 25 (survey seg 3))</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>https://ecode360.com/44006773</t>
+          <t>https://www.delmar.ca.us/AgendaCenter/ViewFile/Agenda/_09142026-3926</t>
         </is>
       </c>
       <c r="V30">
@@ -3522,7 +3478,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 30 mph (OSM/imagery: osm 20)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 45)</t>
         </is>
       </c>
       <c r="Y30" t="n">
@@ -3530,62 +3486,60 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>185</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CBD-B1-030</t>
+          <t>DMR-B1-004</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Del Mar</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Carlsbad Boulevard</t>
+          <t>Camino del Mar</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mountain View Drive</t>
+          <t>Sandy Lane</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Cypress Avenue</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1085300499</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>30</v>
-      </c>
+          <t>34906973</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>inferred</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.162771,-117.354398&amp;heading=171</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.975522,-117.269016&amp;heading=352</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.162771,-117.354398</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.975522,-117.269016</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -3599,21 +3553,9 @@
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Carlsbad Blvd (State St - Tamarack Ave)</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>https://ecode360.com/44006773</t>
-        </is>
-      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
       <c r="V31">
         <f>IF(OR(L31="",S31=""),"",IF(VALUE(L31)=VALUE(S31),"Y","N"))</f>
         <v/>
@@ -3624,7 +3566,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 30 mph (OSM/imagery: mapillary 25)</t>
+          <t>sources disagree: sources disagree (news 30, mapillary 25); map shows None</t>
         </is>
       </c>
       <c r="Y31" t="n">
@@ -3632,39 +3574,39 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>185</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CBD-B1-031</t>
+          <t>DMR-B1-005</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Del Mar</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Carlsbad Boulevard</t>
+          <t>Camino del Mar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>Border Avenue</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Mountain View Drive</t>
+          <t>Sandy Lane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>526970380</t>
+          <t>157531225</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -3672,7 +3614,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3682,12 +3624,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.165740,-117.354582&amp;heading=172</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.977038,-117.269310&amp;heading=175</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.165740,-117.354582</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.977038,-117.269310</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -3701,21 +3643,9 @@
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Carlsbad Blvd (State St - Tamarack Ave)</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>https://ecode360.com/44006773</t>
-        </is>
-      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32">
         <f>IF(OR(L32="",S32=""),"",IF(VALUE(L32)=VALUE(S32),"Y","N"))</f>
         <v/>
@@ -3726,55 +3656,55 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 30 mph (OSM/imagery: osm 15)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 45, news 30); map shows 30</t>
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>253</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CBD-B1-032</t>
+          <t>DMR-B1-006</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Del Mar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Carlsbad Boulevard</t>
+          <t>Camino del Mar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>Border Avenue</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mountain View Drive</t>
+          <t>Sandy Lane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>794576109</t>
+          <t>157531218</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3784,12 +3714,12 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.165909,-117.354569&amp;heading=167</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.979313,-117.269209&amp;heading=185</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.165909,-117.354569</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.979313,-117.269209</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -3803,21 +3733,9 @@
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>Carlsbad Blvd (North city limit - State St)</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>https://ecode360.com/44006773</t>
-        </is>
-      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
       <c r="V33">
         <f>IF(OR(L33="",S33=""),"",IF(VALUE(L33)=VALUE(S33),"Y","N"))</f>
         <v/>
@@ -3828,47 +3746,47 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 10)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 45, news 30, mapillary 40); map shows 30</t>
         </is>
       </c>
       <c r="Y33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>220</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CBD-B1-033</t>
+          <t>ENC-B1-001</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Encinitas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Carlsbad Boulevard</t>
+          <t>Encinitas Boulevard</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>North Vulcan Avenue</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Mountain View Drive</t>
+          <t>B Street</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>382185424</t>
+          <t>169543038</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -3886,12 +3804,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.166139,-117.354677&amp;heading=155</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.048784,-117.294009&amp;heading=265</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.166139,-117.354677</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.048784,-117.294009</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -3912,12 +3830,12 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (North city limit - State St)</t>
+          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Encinitas Blvd (Coast Hwy 101 - Quail Gardens Rd) posted 35</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>https://ecode360.com/44006773</t>
+          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
         </is>
       </c>
       <c r="V34">
@@ -3930,7 +3848,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 15)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 35 mph (OSM/imagery: osm 40)</t>
         </is>
       </c>
       <c r="Y34" t="n">
@@ -3938,39 +3856,39 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CBD-B1-034</t>
+          <t>ENC-B1-002</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Encinitas</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Carlsbad Boulevard</t>
+          <t>Encinitas Boulevard</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>North Vulcan Avenue</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mountain View Drive</t>
+          <t>B Street</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>407600254</t>
+          <t>391854306</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -3988,12 +3906,12 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.166569,-117.354912&amp;heading=145</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.048805,-117.293719&amp;heading=265</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.166569,-117.354912</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.048805,-117.293719</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4014,12 +3932,12 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Carlsbad Blvd (North city limit - State St)</t>
+          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Encinitas Blvd (Coast Hwy 101 - Quail Gardens Rd) posted 35</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>https://ecode360.com/44006773</t>
+          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
         </is>
       </c>
       <c r="V35">
@@ -4032,7 +3950,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 25)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 35 mph (OSM/imagery: osm 40)</t>
         </is>
       </c>
       <c r="Y35" t="n">
@@ -4040,43 +3958,43 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CBD-B1-035</t>
+          <t>ENC-B1-003</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Encinitas</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>La Costa Avenue</t>
+          <t>Encinitas Boulevard</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>North Vulcan Avenue</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>North Vulcan Avenue</t>
+          <t>B Street</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>750625054</t>
+          <t>391854304</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -4090,12 +4008,12 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.082615,-117.308638&amp;heading=50</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.048823,-117.293482&amp;heading=265</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.082615,-117.308638</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.048823,-117.293482</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4111,12 +4029,12 @@
       <c r="R36" t="inlineStr"/>
       <c r="S36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): La Costa Ave (N Coast Hwy 101 - East City Limits) posted 30</t>
+          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Encinitas Blvd (Coast Hwy 101 - Quail Gardens Rd) posted 35</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4134,7 +4052,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 30 mph (OSM/imagery: osm 40)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 35 mph (OSM/imagery: osm 40)</t>
         </is>
       </c>
       <c r="Y36" t="n">
@@ -4142,39 +4060,39 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>9</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CBD-B1-036</t>
+          <t>ENC-B1-004</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Carlsbad</t>
+          <t>Encinitas</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>Encinitas Boulevard</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Pacific Coast Highway</t>
+          <t>North Vulcan Avenue</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Pacific Coast Highway</t>
+          <t>B Street</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>436435229</t>
+          <t>391854305</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -4192,12 +4110,12 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.171797,-117.359296&amp;heading=148</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.048845,-117.293162&amp;heading=265</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.171797,-117.359296</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.048845,-117.293162</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -4218,12 +4136,12 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Coast Highway (Wisconsin Ave - south city limit)</t>
+          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Encinitas Blvd (Coast Hwy 101 - Quail Gardens Rd) posted 35</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>https://gocodebook.com/library/us/ca/oceanside/oceanside-traffic-code-1/article-xiv-special-speed-zones</t>
+          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
         </is>
       </c>
       <c r="V37">
@@ -4236,7 +4154,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 35 mph (OSM/imagery: osm 40)</t>
         </is>
       </c>
       <c r="Y37" t="n">
@@ -4244,39 +4162,39 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DMR-B1-001</t>
+          <t>ENC-B1-005</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Del Mar</t>
+          <t>Encinitas</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Camino del Mar</t>
+          <t>North Coast Highway</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>27th Street</t>
+          <t>B Street</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sandy Pointe</t>
+          <t>A Street</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1342043490</t>
+          <t>436300808</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -4294,12 +4212,12 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.971681,-117.268312&amp;heading=351</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.049737,-117.294331&amp;heading=353</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.971681,-117.268312</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.049737,-117.294331</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -4320,12 +4238,12 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Camino del Mar (San Dieguito Bridge - Coast Blvd: posted 25 (survey seg 3))</t>
+          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>https://www.delmar.ca.us/AgendaCenter/ViewFile/Agenda/_09142026-3926</t>
+          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
         </is>
       </c>
       <c r="V38">
@@ -4338,7 +4256,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: mapillary 30)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
         </is>
       </c>
       <c r="Y38" t="n">
@@ -4346,43 +4264,43 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>46</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DMR-B1-002</t>
+          <t>ENC-B1-006</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Del Mar</t>
+          <t>Encinitas</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Camino del Mar</t>
+          <t>North Coast Highway</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sandy Lane</t>
+          <t>Athena Street</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>North Coast Highway 101</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>34906973</t>
+          <t>1329263158</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -4391,17 +4309,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.975522,-117.269016&amp;heading=352</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.057724,-117.298978&amp;heading=151</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.975522,-117.269016</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.057724,-117.298978</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -4417,17 +4335,17 @@
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Camino del Mar (Via de la Valle - San Dieguito Bridge — posted 40 mph today; ordinance lowers it to 30 mph from 2026-11-19, once new signs are up)</t>
+          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>https://www.delmar.ca.us/AgendaCenter/ViewFile/Agenda/_10202026-3943</t>
+          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
         </is>
       </c>
       <c r="V39">
@@ -4440,7 +4358,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 40 mph (OSM/imagery: mapillary 25)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
         </is>
       </c>
       <c r="Y39" t="n">
@@ -4448,43 +4366,43 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>162</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DMR-B1-003</t>
+          <t>ENC-B1-007</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Del Mar</t>
+          <t>Encinitas</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Camino del Mar</t>
+          <t>North Coast Highway</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sandy Lane</t>
+          <t>North Coast Highway 101</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>Athena Street</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>157272809</t>
+          <t>436300819</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -4493,17 +4411,17 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.976984,-117.269221&amp;heading=355</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.058245,-117.299291&amp;heading=332</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.976984,-117.269221</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.058245,-117.299291</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -4519,17 +4437,17 @@
       <c r="R40" t="inlineStr"/>
       <c r="S40" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Camino del Mar (Via de la Valle - San Dieguito Bridge — posted 40 mph today; ordinance lowers it to 30 mph from 2026-11-19, once new signs are up)</t>
+          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>https://www.delmar.ca.us/AgendaCenter/ViewFile/Agenda/_10202026-3943</t>
+          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
         </is>
       </c>
       <c r="V40">
@@ -4542,7 +4460,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
         </is>
       </c>
       <c r="Y40" t="n">
@@ -4550,43 +4468,43 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>42</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DMR-B1-004</t>
+          <t>ENC-B1-008</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Del Mar</t>
+          <t>Encinitas</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Camino del Mar</t>
+          <t>North Coast Highway</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Border Avenue</t>
+          <t>Athena Street</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sandy Lane</t>
+          <t>Basil Street</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>157531225</t>
+          <t>436300813</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -4595,17 +4513,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.977038,-117.269310&amp;heading=175</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.059394,-117.300019&amp;heading=332</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.977038,-117.269310</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.059394,-117.300019</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -4621,17 +4539,17 @@
       <c r="R41" t="inlineStr"/>
       <c r="S41" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Camino del Mar (Via de la Valle - San Dieguito Bridge — posted 40 mph today; ordinance lowers it to 30 mph from 2026-11-19, once new signs are up)</t>
+          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>https://www.delmar.ca.us/AgendaCenter/ViewFile/Agenda/_10202026-3943</t>
+          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
         </is>
       </c>
       <c r="V41">
@@ -4644,7 +4562,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 40 mph (OSM/imagery: osm 45)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
         </is>
       </c>
       <c r="Y41" t="n">
@@ -4652,43 +4570,43 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>253</t>
+          <t>33</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DMR-B1-005</t>
+          <t>ENC-B1-009</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Del Mar</t>
+          <t>Encinitas</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Camino del Mar</t>
+          <t>North Coast Highway</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sandy Lane</t>
+          <t>West Leucadia Boulevard</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>Cadmus Street</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>34092357</t>
+          <t>1098265887</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -4697,17 +4615,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.979278,-117.269075&amp;heading=7</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.061804,-117.301410&amp;heading=162</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.979278,-117.269075</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.061804,-117.301410</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -4723,17 +4641,17 @@
       <c r="R42" t="inlineStr"/>
       <c r="S42" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>Camino del Mar (Via de la Valle - San Dieguito Bridge — posted 40 mph today; ordinance lowers it to 30 mph from 2026-11-19, once new signs are up)</t>
+          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>https://www.delmar.ca.us/AgendaCenter/ViewFile/Agenda/_10202026-3943</t>
+          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
         </is>
       </c>
       <c r="V42">
@@ -4746,22 +4664,22 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 35, mapillary 35)</t>
         </is>
       </c>
       <c r="Y42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>418</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ENC-B1-001</t>
+          <t>ENC-B1-010</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4771,26 +4689,26 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Encinitas Boulevard</t>
+          <t>North Coast Highway</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>North Vulcan Avenue</t>
+          <t>West Leucadia Boulevard</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>B Street</t>
+          <t>Europa Street</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>169543038</t>
+          <t>331768745</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4799,17 +4717,17 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.048784,-117.294009&amp;heading=265</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.064400,-117.302321&amp;heading=164</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.048784,-117.294009</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.064400,-117.302321</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -4825,12 +4743,12 @@
       <c r="R43" t="inlineStr"/>
       <c r="S43" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Encinitas Blvd (Coast Hwy 101 - Quail Gardens Rd) posted 35</t>
+          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4848,22 +4766,22 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 40)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 35)</t>
         </is>
       </c>
       <c r="Y43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENC-B1-002</t>
+          <t>ENC-B1-011</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4873,26 +4791,26 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Encinitas Boulevard</t>
+          <t>North Coast Highway</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>North Vulcan Avenue</t>
+          <t>Jupiter Street</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>B Street</t>
+          <t>Diana Street</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>391854306</t>
+          <t>393555889</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -4901,17 +4819,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.048805,-117.293719&amp;heading=265</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.069493,-117.304010&amp;heading=164</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.048805,-117.293719</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.069493,-117.304010</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -4927,12 +4845,12 @@
       <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Encinitas Blvd (Coast Hwy 101 - Quail Gardens Rd) posted 35</t>
+          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -4950,7 +4868,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 40)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
         </is>
       </c>
       <c r="Y44" t="n">
@@ -4958,14 +4876,14 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>587</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENC-B1-003</t>
+          <t>ENC-B1-012</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4975,26 +4893,26 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Encinitas Boulevard</t>
+          <t>North Coast Highway</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>North Vulcan Avenue</t>
+          <t>Bishops Gate Road</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>B Street</t>
+          <t>Grandview Street</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>391854304</t>
+          <t>1031589249</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -5003,17 +4921,17 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.048823,-117.293482&amp;heading=265</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.078607,-117.307051&amp;heading=164</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.048823,-117.293482</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.078607,-117.307051</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -5029,12 +4947,12 @@
       <c r="R45" t="inlineStr"/>
       <c r="S45" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Encinitas Blvd (Coast Hwy 101 - Quail Gardens Rd) posted 35</t>
+          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5052,7 +4970,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 40)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
         </is>
       </c>
       <c r="Y45" t="n">
@@ -5060,14 +4978,14 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ENC-B1-004</t>
+          <t>ENC-B1-013</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5077,26 +4995,26 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Encinitas Boulevard</t>
+          <t>North Coast Highway</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>North Vulcan Avenue</t>
+          <t>Moorgate Road</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>B Street</t>
+          <t>Bishops Gate Road</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>391854305</t>
+          <t>436410539</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -5105,17 +5023,17 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.048845,-117.293162&amp;heading=265</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.079616,-117.307399&amp;heading=164</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.048845,-117.293162</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.079616,-117.307399</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -5131,12 +5049,12 @@
       <c r="R46" t="inlineStr"/>
       <c r="S46" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Encinitas Blvd (Coast Hwy 101 - Quail Gardens Rd) posted 35</t>
+          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5154,7 +5072,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 40)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
         </is>
       </c>
       <c r="Y46" t="n">
@@ -5162,14 +5080,14 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>160</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ENC-B1-005</t>
+          <t>ENC-B1-014</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5184,17 +5102,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>B Street</t>
+          <t>La Costa Avenue</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>A Street</t>
+          <t>Moorgate Road</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>436300808</t>
+          <t>158341851</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -5212,12 +5130,12 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.049737,-117.294331&amp;heading=353</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.081929,-117.308411&amp;heading=149</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.049737,-117.294331</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.081929,-117.308411</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -5256,7 +5174,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
         </is>
       </c>
       <c r="Y47" t="n">
@@ -5264,14 +5182,14 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>167</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ENC-B1-006</t>
+          <t>ENC-B1-015</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5281,45 +5199,45 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Athena Street</t>
+          <t>Cardiff State Beach</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>North Coast Highway 101</t>
+          <t>Ocean Street</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1329263158</t>
+          <t>5971449</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>inferred</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.057724,-117.298978&amp;heading=151</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.000172,-117.275238&amp;heading=139</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.057724,-117.298978</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.000172,-117.275238</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -5333,21 +5251,9 @@
       </c>
       <c r="Q48" t="inlineStr"/>
       <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
-        </is>
-      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
       <c r="V48">
         <f>IF(OR(L48="",S48=""),"",IF(VALUE(L48)=VALUE(S48),"Y","N"))</f>
         <v/>
@@ -5358,7 +5264,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (streetview 30, mapillary 40); map shows 30</t>
         </is>
       </c>
       <c r="Y48" t="n">
@@ -5366,14 +5272,14 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>230</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ENC-B1-007</t>
+          <t>ENC-B1-016</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5383,45 +5289,45 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>North Coast Highway 101</t>
+          <t>Ocean Street</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Athena Street</t>
+          <t>Cardiff State Beach</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>436300819</t>
+          <t>436403305</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.058245,-117.299291&amp;heading=332</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.002113,-117.276978&amp;heading=328</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.058245,-117.299291</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.002113,-117.276978</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -5435,21 +5341,9 @@
       </c>
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
-        </is>
-      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
       <c r="V49">
         <f>IF(OR(L49="",S49=""),"",IF(VALUE(L49)=VALUE(S49),"Y","N"))</f>
         <v/>
@@ -5460,7 +5354,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 30, streetview 30, mapillary 45); map shows 30</t>
         </is>
       </c>
       <c r="Y49" t="n">
@@ -5468,14 +5362,14 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>103</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ENC-B1-008</t>
+          <t>ENC-B1-017</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5485,45 +5379,45 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Athena Street</t>
+          <t>Ocean Street</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Basil Street</t>
+          <t>Cardiff State Beach</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1106587666</t>
+          <t>5963768</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.059240,-117.299922&amp;heading=332</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.006962,-117.278351&amp;heading=354</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.059240,-117.299922</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.006962,-117.278351</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -5537,21 +5431,9 @@
       </c>
       <c r="Q50" t="inlineStr"/>
       <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
-        </is>
-      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
       <c r="V50">
         <f>IF(OR(L50="",S50=""),"",IF(VALUE(L50)=VALUE(S50),"Y","N"))</f>
         <v/>
@@ -5562,7 +5444,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 30, streetview 30, mapillary 45); map shows 30</t>
         </is>
       </c>
       <c r="Y50" t="n">
@@ -5570,14 +5452,14 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>817</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ENC-B1-009</t>
+          <t>ENC-B1-018</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5587,45 +5469,45 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Athena Street</t>
+          <t>Ocean Street</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Basil Street</t>
+          <t>Cardiff State Beach</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>436300813</t>
+          <t>436402237</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.059394,-117.300019&amp;heading=332</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.013835,-117.280000&amp;heading=343</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.059394,-117.300019</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.013835,-117.280000</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -5639,21 +5521,9 @@
       </c>
       <c r="Q51" t="inlineStr"/>
       <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
-        </is>
-      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
       <c r="V51">
         <f>IF(OR(L51="",S51=""),"",IF(VALUE(L51)=VALUE(S51),"Y","N"))</f>
         <v/>
@@ -5664,7 +5534,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 30, streetview 30, mapillary 45); map shows 30</t>
         </is>
       </c>
       <c r="Y51" t="n">
@@ -5672,14 +5542,14 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>39</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ENC-B1-010</t>
+          <t>ENC-B1-019</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5689,45 +5559,45 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Basil Street</t>
+          <t>Cardiff State Beach</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cadmus Street</t>
+          <t>Chesterfield Drive</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>211570987</t>
+          <t>436402239</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.059847,-117.300320&amp;heading=334</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.018937,-117.282272&amp;heading=336</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.059847,-117.300320</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.018937,-117.282272</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -5741,21 +5611,9 @@
       </c>
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
-        </is>
-      </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
       <c r="V52">
         <f>IF(OR(L52="",S52=""),"",IF(VALUE(L52)=VALUE(S52),"Y","N"))</f>
         <v/>
@@ -5766,7 +5624,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 30, streetview 30, mapillary 45); map shows 30</t>
         </is>
       </c>
       <c r="Y52" t="n">
@@ -5774,14 +5632,14 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>73</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ENC-B1-011</t>
+          <t>ENC-B1-020</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5791,45 +5649,45 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>West Leucadia Boulevard</t>
+          <t>Chesterfield Drive</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cadmus Street</t>
+          <t>West K Street</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1098265887</t>
+          <t>436402235</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.061804,-117.301410&amp;heading=162</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.026772,-117.286982&amp;heading=333</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.061804,-117.301410</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.026772,-117.286982</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -5843,21 +5701,9 @@
       </c>
       <c r="Q53" t="inlineStr"/>
       <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
-        </is>
-      </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
       <c r="V53">
         <f>IF(OR(L53="",S53=""),"",IF(VALUE(L53)=VALUE(S53),"Y","N"))</f>
         <v/>
@@ -5868,22 +5714,22 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: osm 35, mapillary 35)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 30, streetview 30, mapillary 45); map shows 30</t>
         </is>
       </c>
       <c r="Y53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>80</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ENC-B1-012</t>
+          <t>ENC-B1-021</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5893,22 +5739,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>West Leucadia Boulevard</t>
+          <t>West K Street</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Europa Street</t>
+          <t>Chesterfield Drive</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>331768745</t>
+          <t>830832325</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -5926,12 +5772,12 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.064400,-117.302321&amp;heading=164</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.035859,-117.291823&amp;heading=158</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.064400,-117.302321</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.035859,-117.291823</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -5952,7 +5798,7 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
+          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -5970,22 +5816,22 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: osm 35)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 30, mapillary 45)</t>
         </is>
       </c>
       <c r="Y54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>132</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ENC-B1-013</t>
+          <t>ENC-B1-022</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5995,22 +5841,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Jasper Street</t>
+          <t>West K Street</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>West Leucadia Boulevard</t>
+          <t>Chesterfield Drive</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>436410528</t>
+          <t>926055270</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -6028,12 +5874,12 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.064478,-117.302349&amp;heading=165</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.035955,-117.291871&amp;heading=157</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.064478,-117.302349</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.035955,-117.291871</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -6054,7 +5900,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
+          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6072,22 +5918,22 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 30)</t>
         </is>
       </c>
       <c r="Y55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>111</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ENC-B1-014</t>
+          <t>ENC-B1-023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6097,22 +5943,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Diana Street</t>
+          <t>West I Street</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>West Leucadia Boulevard</t>
+          <t>West K Street</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1106585108</t>
+          <t>437779286</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -6130,12 +5976,12 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.065616,-117.302738&amp;heading=165</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.038117,-117.292785&amp;heading=174</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.065616,-117.302738</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.038117,-117.292785</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -6156,7 +6002,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
+          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6174,7 +6020,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 25, mapillary 30)</t>
         </is>
       </c>
       <c r="Y56" t="n">
@@ -6182,14 +6028,14 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>172</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ENC-B1-015</t>
+          <t>ENC-B1-024</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6199,22 +6045,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Jupiter Street</t>
+          <t>West H Street</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Diana Street</t>
+          <t>West I Street</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>393555889</t>
+          <t>436442869</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -6232,12 +6078,12 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.069493,-117.304010&amp;heading=164</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.039912,-117.293019&amp;heading=174</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.069493,-117.304010</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.039912,-117.293019</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -6258,7 +6104,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
+          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6276,22 +6122,22 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 25, mapillary 30)</t>
         </is>
       </c>
       <c r="Y57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>110</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ENC-B1-016</t>
+          <t>ENC-B1-025</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6301,22 +6147,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Grandview Street</t>
+          <t>West G Street</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Jupiter Street</t>
+          <t>West H Street</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1457602672</t>
+          <t>436442870</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -6334,12 +6180,12 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.073880,-117.305482&amp;heading=164</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.041439,-117.293227&amp;heading=173</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.073880,-117.305482</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.041439,-117.293227</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -6360,7 +6206,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
+          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6378,22 +6224,22 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 25, mapillary 30)</t>
         </is>
       </c>
       <c r="Y58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>411</t>
+          <t>74</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ENC-B1-017</t>
+          <t>ENC-B1-026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6403,22 +6249,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Bishops Gate Road</t>
+          <t>West F Street</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Grandview Street</t>
+          <t>West G Street</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1031589250</t>
+          <t>436442868</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -6436,12 +6282,12 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.077448,-117.306662&amp;heading=164</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.042933,-117.293434&amp;heading=173</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.077448,-117.306662</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.042933,-117.293434</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -6462,7 +6308,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
+          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6480,22 +6326,22 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 25, mapillary 30)</t>
         </is>
       </c>
       <c r="Y59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>61</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ENC-B1-018</t>
+          <t>ENC-B1-027</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6505,22 +6351,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Bishops Gate Road</t>
+          <t>East E Street</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Grandview Street</t>
+          <t>West F Street</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1031589249</t>
+          <t>1022281192</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -6538,12 +6384,12 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.078607,-117.307051&amp;heading=164</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.043362,-117.293488&amp;heading=173</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.078607,-117.307051</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.043362,-117.293488</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -6564,7 +6410,7 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
+          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6582,22 +6428,22 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 30)</t>
         </is>
       </c>
       <c r="Y60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ENC-B1-019</t>
+          <t>ENC-B1-028</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6607,22 +6453,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Moorgate Road</t>
+          <t>East E Street</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bishops Gate Road</t>
+          <t>West F Street</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>436410539</t>
+          <t>436442867</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -6640,12 +6486,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.079616,-117.307399&amp;heading=164</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.043461,-117.293501&amp;heading=173</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.079616,-117.307399</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.043461,-117.293501</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -6666,7 +6512,7 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
+          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6684,22 +6530,22 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 30)</t>
         </is>
       </c>
       <c r="Y61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ENC-B1-020</t>
+          <t>ENC-B1-029</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6709,22 +6555,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>La Costa Avenue</t>
+          <t>East E Street</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Moorgate Road</t>
+          <t>West F Street</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>794576108</t>
+          <t>960133747</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -6742,12 +6588,12 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.080814,-117.307798&amp;heading=159</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.044589,-117.293659&amp;heading=173</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.080814,-117.307798</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.044589,-117.293659</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -6768,7 +6614,7 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
+          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -6786,22 +6632,22 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: osm 30)</t>
         </is>
       </c>
       <c r="Y62" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>96</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ENC-B1-021</t>
+          <t>ENC-B1-030</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6811,26 +6657,26 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>North Coast Highway</t>
+          <t>South Vulcan Avenue</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>La Costa Avenue</t>
+          <t>Encinitas Boulevard</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Moorgate Road</t>
+          <t>East D Street</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>158341851</t>
+          <t>1245123396</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -6839,17 +6685,17 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.081929,-117.308411&amp;heading=149</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.046944,-117.292727&amp;heading=174</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.081929,-117.308411</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.046944,-117.292727</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -6865,12 +6711,12 @@
       <c r="R63" t="inlineStr"/>
       <c r="S63" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>N Coast Hwy 101 (La Costa Ave - Encinitas Blvd)</t>
+          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Vulcan Ave (Encinitas Blvd - Santa Fe Dr) posted 30</t>
         </is>
       </c>
       <c r="U63" t="inlineStr">
@@ -6888,7 +6734,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 30 mph (OSM/imagery: osm 40)</t>
         </is>
       </c>
       <c r="Y63" t="n">
@@ -6896,14 +6742,14 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ENC-B1-022</t>
+          <t>ENC-B1-031</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6913,26 +6759,26 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>South Vulcan Avenue</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>West K Street</t>
+          <t>Encinitas Boulevard</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chesterfield Drive</t>
+          <t>East D Street</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>830832325</t>
+          <t>1245123397</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -6941,17 +6787,17 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.035859,-117.291823&amp;heading=158</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.047220,-117.292762&amp;heading=174</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.035859,-117.291823</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.047220,-117.292762</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -6967,12 +6813,12 @@
       <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
+          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Vulcan Ave (Encinitas Blvd - Santa Fe Dr) posted 30</t>
         </is>
       </c>
       <c r="U64" t="inlineStr">
@@ -6990,22 +6836,22 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: osm 30, mapillary 45)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 30 mph (OSM/imagery: osm 40)</t>
         </is>
       </c>
       <c r="Y64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>85</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ENC-B1-023</t>
+          <t>ENC-B1-032</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7015,26 +6861,26 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>South Vulcan Avenue</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>West K Street</t>
+          <t>Encinitas Boulevard</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chesterfield Drive</t>
+          <t>East D Street</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>926055270</t>
+          <t>6001345</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -7043,17 +6889,17 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.035955,-117.291871&amp;heading=157</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.048530,-117.292927&amp;heading=174</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.035955,-117.291871</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.048530,-117.292927</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -7069,12 +6915,12 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
+          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Vulcan Ave (Encinitas Blvd - Santa Fe Dr) posted 30</t>
         </is>
       </c>
       <c r="U65" t="inlineStr">
@@ -7092,51 +6938,51 @@
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: osm 30)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 30 mph (OSM/imagery: osm 40)</t>
         </is>
       </c>
       <c r="Y65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>109</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ENC-B1-024</t>
+          <t>IMB-B1-001</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Encinitas</t>
+          <t>Imperial Beach</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>Seacoast Drive</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>East E Street</t>
+          <t>Ebony Avenue</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>West F Street</t>
+          <t>Imperial Beach Boulevard</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>1022281192</t>
+          <t>1349741397</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -7150,12 +6996,12 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.043362,-117.293488&amp;heading=173</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.576645,-117.131737&amp;heading=180</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.043362,-117.293488</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.576645,-117.131737</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -7171,17 +7017,17 @@
       <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
+          <t>Seacoast Dr (Palm Ave - Imperial Beach Blvd)</t>
         </is>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
+          <t>https://pub-imperialbeach.escribemeetings.com/filestream.ashx?DocumentId=973</t>
         </is>
       </c>
       <c r="V66">
@@ -7194,51 +7040,51 @@
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: osm 30)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 20 mph (OSM/imagery: osm 25)</t>
         </is>
       </c>
       <c r="Y66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ENC-B1-025</t>
+          <t>IMB-B1-002</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Encinitas</t>
+          <t>Imperial Beach</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>Seacoast Drive</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>East E Street</t>
+          <t>Elkwood Avenue</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>West F Street</t>
+          <t>Imperial Beach Boulevard</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>436442867</t>
+          <t>1349741538</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -7252,12 +7098,12 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.043461,-117.293501&amp;heading=173</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.577028,-117.131737&amp;heading=180</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.043461,-117.293501</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.577028,-117.131737</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -7273,17 +7119,17 @@
       <c r="R67" t="inlineStr"/>
       <c r="S67" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
+          <t>Seacoast Dr (Palm Ave - Imperial Beach Blvd)</t>
         </is>
       </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
+          <t>https://pub-imperialbeach.escribemeetings.com/filestream.ashx?DocumentId=973</t>
         </is>
       </c>
       <c r="V67">
@@ -7296,51 +7142,51 @@
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: osm 30)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 20 mph (OSM/imagery: osm 25, mapillary 25)</t>
         </is>
       </c>
       <c r="Y67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>147</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ENC-B1-026</t>
+          <t>IMB-B1-003</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Encinitas</t>
+          <t>Imperial Beach</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>Seacoast Drive</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>East E Street</t>
+          <t>Elder Avenue</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>West F Street</t>
+          <t>Ebony Avenue</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>960133747</t>
+          <t>1349741537</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -7354,12 +7200,12 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.044589,-117.293659&amp;heading=173</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.578121,-117.131732&amp;heading=180</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.044589,-117.293659</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.578121,-117.131732</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -7375,17 +7221,17 @@
       <c r="R68" t="inlineStr"/>
       <c r="S68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>S Coast Hwy 101 (Encinitas Blvd - Swami's Ped Crossing)</t>
+          <t>Seacoast Dr (Palm Ave - Imperial Beach Blvd)</t>
         </is>
       </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
+          <t>https://pub-imperialbeach.escribemeetings.com/filestream.ashx?DocumentId=973</t>
         </is>
       </c>
       <c r="V68">
@@ -7398,51 +7244,51 @@
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: osm 30)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 20 mph (OSM/imagery: osm 25)</t>
         </is>
       </c>
       <c r="Y68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ENC-B1-027</t>
+          <t>IMB-B1-004</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Encinitas</t>
+          <t>Imperial Beach</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>South Vulcan Avenue</t>
+          <t>Seacoast Drive</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Encinitas Boulevard</t>
+          <t>Date Avenue</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>East D Street</t>
+          <t>Elkwood Avenue</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1245123396</t>
+          <t>1349741828</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -7451,17 +7297,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.046944,-117.292727&amp;heading=174</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.579568,-117.131727&amp;heading=180</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.046944,-117.292727</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.579568,-117.131727</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -7477,17 +7323,17 @@
       <c r="R69" t="inlineStr"/>
       <c r="S69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Vulcan Ave (Encinitas Blvd - Santa Fe Dr) posted 30</t>
+          <t>Seacoast Dr (Palm Ave - Imperial Beach Blvd)</t>
         </is>
       </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
+          <t>https://pub-imperialbeach.escribemeetings.com/filestream.ashx?DocumentId=973</t>
         </is>
       </c>
       <c r="V69">
@@ -7500,51 +7346,51 @@
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 30 mph (OSM/imagery: osm 40)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 20 mph (OSM/imagery: osm 25)</t>
         </is>
       </c>
       <c r="Y69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>307</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ENC-B1-028</t>
+          <t>IMB-B1-005</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Encinitas</t>
+          <t>Imperial Beach</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>South Vulcan Avenue</t>
+          <t>Seacoast Drive</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Encinitas Boulevard</t>
+          <t>Daisy Avenue</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>East D Street</t>
+          <t>Elm Avenue</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1245123397</t>
+          <t>1349741827</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -7553,17 +7399,17 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.047220,-117.292762&amp;heading=174</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.581003,-117.131727&amp;heading=179</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.047220,-117.292762</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.581003,-117.131727</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -7579,17 +7425,17 @@
       <c r="R70" t="inlineStr"/>
       <c r="S70" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Vulcan Ave (Encinitas Blvd - Santa Fe Dr) posted 30</t>
+          <t>Seacoast Dr (Palm Ave - Imperial Beach Blvd)</t>
         </is>
       </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
+          <t>https://pub-imperialbeach.escribemeetings.com/filestream.ashx?DocumentId=973</t>
         </is>
       </c>
       <c r="V70">
@@ -7602,7 +7448,7 @@
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 30 mph (OSM/imagery: osm 40)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 20 mph (OSM/imagery: osm 25)</t>
         </is>
       </c>
       <c r="Y70" t="n">
@@ -7610,43 +7456,43 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ENC-B1-029</t>
+          <t>IMB-B1-006</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Encinitas</t>
+          <t>Imperial Beach</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>South Vulcan Avenue</t>
+          <t>Seacoast Drive</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Encinitas Boulevard</t>
+          <t>Daisy Avenue</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>East D Street</t>
+          <t>Date Avenue</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>6001345</t>
+          <t>1349741898</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -7655,17 +7501,17 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.048530,-117.292927&amp;heading=174</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.581373,-117.131727&amp;heading=180</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.048530,-117.292927</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.581373,-117.131727</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -7681,17 +7527,17 @@
       <c r="R71" t="inlineStr"/>
       <c r="S71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Encinitas Ord. 2026-05 Exhibit A (2026 E&amp;TS): Vulcan Ave (Encinitas Blvd - Santa Fe Dr) posted 30</t>
+          <t>Seacoast Dr (Palm Ave - Imperial Beach Blvd)</t>
         </is>
       </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>https://ecode360.com/EN5042/laws/LF2740111.pdf</t>
+          <t>https://pub-imperialbeach.escribemeetings.com/filestream.ashx?DocumentId=973</t>
         </is>
       </c>
       <c r="V71">
@@ -7704,7 +7550,7 @@
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 30 mph (OSM/imagery: osm 40)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 20 mph (OSM/imagery: osm 25)</t>
         </is>
       </c>
       <c r="Y71" t="n">
@@ -7712,14 +7558,14 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IMB-B1-001</t>
+          <t>IMB-B1-007</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -7734,17 +7580,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ebony Avenue</t>
+          <t>Donax Avenue</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Imperial Beach Boulevard</t>
+          <t>Date Avenue</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>1349741397</t>
+          <t>1349741897</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -7762,12 +7608,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.576645,-117.131737&amp;heading=180</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.581745,-117.131726&amp;heading=180</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.576645,-117.131737</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.581745,-117.131726</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -7806,7 +7652,7 @@
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 20 mph (OSM/imagery: osm 25)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 20 mph (OSM/imagery: osm 25)</t>
         </is>
       </c>
       <c r="Y72" t="n">
@@ -7814,14 +7660,14 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IMB-B1-002</t>
+          <t>IMB-B1-008</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7836,17 +7682,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Elkwood Avenue</t>
+          <t>Palm Avenue</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Imperial Beach Boulevard</t>
+          <t>Daisy Avenue</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>1349741538</t>
+          <t>149560905</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -7864,12 +7710,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.577028,-117.131737&amp;heading=180</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.582460,-117.131730&amp;heading=179</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.577028,-117.131737</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.582460,-117.131730</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -7908,7 +7754,7 @@
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 20 mph (OSM/imagery: osm 25, mapillary 25)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 20 mph (OSM/imagery: osm 25)</t>
         </is>
       </c>
       <c r="Y73" t="n">
@@ -7916,47 +7762,47 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>226</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IMB-B1-003</t>
+          <t>LJA-B1-001</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Imperial Beach</t>
+          <t>La Jolla</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Seacoast Drive</t>
+          <t>La Jolla Boulevard</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Elder Avenue</t>
+          <t>Carla Way</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ebony Avenue</t>
+          <t>Colima Street</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1349741537</t>
+          <t>6055286</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -7966,12 +7812,12 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.578121,-117.131732&amp;heading=180</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.809405,-117.264651&amp;heading=318</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.578121,-117.131732</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.809405,-117.264651</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -7985,21 +7831,9 @@
       </c>
       <c r="Q74" t="inlineStr"/>
       <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Seacoast Dr (Palm Ave - Imperial Beach Blvd)</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>https://pub-imperialbeach.escribemeetings.com/filestream.ashx?DocumentId=973</t>
-        </is>
-      </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
       <c r="V74">
         <f>IF(OR(L74="",S74=""),"",IF(VALUE(L74)=VALUE(S74),"Y","N"))</f>
         <v/>
@@ -8010,7 +7844,7 @@
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 20 mph (OSM/imagery: osm 25)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 35, news 25); map shows 25</t>
         </is>
       </c>
       <c r="Y74" t="n">
@@ -8018,47 +7852,47 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>24</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IMB-B1-004</t>
+          <t>LJA-B1-002</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Imperial Beach</t>
+          <t>La Jolla</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seacoast Drive</t>
+          <t>La Jolla Boulevard</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Date Avenue</t>
+          <t>Carla Way</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Elkwood Avenue</t>
+          <t>Colima Street</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1349741828</t>
+          <t>436402150</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8068,12 +7902,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.579568,-117.131727&amp;heading=180</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.809543,-117.264827&amp;heading=312</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.579568,-117.131727</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.809543,-117.264827</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -8087,21 +7921,9 @@
       </c>
       <c r="Q75" t="inlineStr"/>
       <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Seacoast Dr (Palm Ave - Imperial Beach Blvd)</t>
-        </is>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>https://pub-imperialbeach.escribemeetings.com/filestream.ashx?DocumentId=973</t>
-        </is>
-      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
       <c r="V75">
         <f>IF(OR(L75="",S75=""),"",IF(VALUE(L75)=VALUE(S75),"Y","N"))</f>
         <v/>
@@ -8112,55 +7934,55 @@
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 20 mph (OSM/imagery: osm 25)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 35, news 25); map shows 25</t>
         </is>
       </c>
       <c r="Y75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>12</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>IMB-B1-005</t>
+          <t>LJA-B1-003</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Imperial Beach</t>
+          <t>La Jolla</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seacoast Drive</t>
+          <t>La Jolla Boulevard</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Daisy Avenue</t>
+          <t>Carla Way</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Elm Avenue</t>
+          <t>Colima Street</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1349741827</t>
+          <t>1090776665</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -8170,12 +7992,12 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.581003,-117.131727&amp;heading=179</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.809721,-117.265036&amp;heading=315</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.581003,-117.131727</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.809721,-117.265036</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -8189,21 +8011,9 @@
       </c>
       <c r="Q76" t="inlineStr"/>
       <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>Seacoast Dr (Palm Ave - Imperial Beach Blvd)</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>https://pub-imperialbeach.escribemeetings.com/filestream.ashx?DocumentId=973</t>
-        </is>
-      </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
       <c r="V76">
         <f>IF(OR(L76="",S76=""),"",IF(VALUE(L76)=VALUE(S76),"Y","N"))</f>
         <v/>
@@ -8214,7 +8024,7 @@
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 20 mph (OSM/imagery: osm 25)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 35, news 25); map shows 25</t>
         </is>
       </c>
       <c r="Y76" t="n">
@@ -8222,47 +8032,47 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IMB-B1-006</t>
+          <t>LJA-B1-004</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Imperial Beach</t>
+          <t>La Jolla</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seacoast Drive</t>
+          <t>La Jolla Boulevard</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Daisy Avenue</t>
+          <t>Carla Way</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Date Avenue</t>
+          <t>Colima Street</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1349741898</t>
+          <t>1427018603</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -8272,12 +8082,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.581373,-117.131727&amp;heading=180</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.810119,-117.265505&amp;heading=315</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.581373,-117.131727</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.810119,-117.265505</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -8291,21 +8101,9 @@
       </c>
       <c r="Q77" t="inlineStr"/>
       <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
-        <is>
-          <t>Seacoast Dr (Palm Ave - Imperial Beach Blvd)</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>https://pub-imperialbeach.escribemeetings.com/filestream.ashx?DocumentId=973</t>
-        </is>
-      </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
       <c r="V77">
         <f>IF(OR(L77="",S77=""),"",IF(VALUE(L77)=VALUE(S77),"Y","N"))</f>
         <v/>
@@ -8316,7 +8114,7 @@
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 20 mph (OSM/imagery: osm 25)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 35, news 25); map shows 25</t>
         </is>
       </c>
       <c r="Y77" t="n">
@@ -8324,47 +8122,47 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>62</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>IMB-B1-007</t>
+          <t>LJA-B1-005</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Imperial Beach</t>
+          <t>La Jolla</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seacoast Drive</t>
+          <t>La Jolla Boulevard</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Donax Avenue</t>
+          <t>Carla Way</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Date Avenue</t>
+          <t>Colima Street</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>1349741897</t>
+          <t>204762551</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -8374,12 +8172,12 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.581745,-117.131726&amp;heading=180</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.810674,-117.266158&amp;heading=315</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.581745,-117.131726</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.810674,-117.266158</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -8393,21 +8191,9 @@
       </c>
       <c r="Q78" t="inlineStr"/>
       <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Seacoast Dr (Palm Ave - Imperial Beach Blvd)</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>https://pub-imperialbeach.escribemeetings.com/filestream.ashx?DocumentId=973</t>
-        </is>
-      </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
       <c r="V78">
         <f>IF(OR(L78="",S78=""),"",IF(VALUE(L78)=VALUE(S78),"Y","N"))</f>
         <v/>
@@ -8418,7 +8204,7 @@
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 20 mph (OSM/imagery: osm 25)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 35, news 25, mapillary 35); map shows 25</t>
         </is>
       </c>
       <c r="Y78" t="n">
@@ -8426,47 +8212,47 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>87</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>IMB-B1-008</t>
+          <t>LJA-B1-006</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Imperial Beach</t>
+          <t>La Jolla</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Seacoast Drive</t>
+          <t>La Jolla Boulevard</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Palm Avenue</t>
+          <t>Carla Way</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Daisy Avenue</t>
+          <t>Colima Street</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>149560905</t>
+          <t>1090776664</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8476,12 +8262,12 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.582460,-117.131730&amp;heading=179</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.810767,-117.266253&amp;heading=319</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.582460,-117.131730</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.810767,-117.266253</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -8495,21 +8281,9 @@
       </c>
       <c r="Q79" t="inlineStr"/>
       <c r="R79" t="inlineStr"/>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
-        <is>
-          <t>Seacoast Dr (Palm Ave - Imperial Beach Blvd)</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>https://pub-imperialbeach.escribemeetings.com/filestream.ashx?DocumentId=973</t>
-        </is>
-      </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
       <c r="V79">
         <f>IF(OR(L79="",S79=""),"",IF(VALUE(L79)=VALUE(S79),"Y","N"))</f>
         <v/>
@@ -8520,7 +8294,7 @@
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 20 mph (OSM/imagery: osm 25)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 35, news 25); map shows 25</t>
         </is>
       </c>
       <c r="Y79" t="n">
@@ -8528,62 +8302,62 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>14</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>OCN-B1-001</t>
+          <t>LJA-B1-007</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Oceanside</t>
+          <t>La Jolla</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>Prospect Street</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cassidy Street</t>
+          <t>Girard Avenue</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pacific Coast Highway</t>
+          <t>Herschel Avenue</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>436403817</t>
+          <t>281630532</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>inferred</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>LSV</t>
+          <t>cart+LSV</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.174986,-117.361986&amp;heading=145</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.847736,-117.274453&amp;heading=217</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.174986,-117.361986</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.847736,-117.274453</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -8597,21 +8371,9 @@
       </c>
       <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>Coast Highway (Wisconsin Ave - south city limit)</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>https://gocodebook.com/library/us/ca/oceanside/oceanside-traffic-code-1/article-xiv-special-speed-zones</t>
-        </is>
-      </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
       <c r="V80">
         <f>IF(OR(L80="",S80=""),"",IF(VALUE(L80)=VALUE(S80),"Y","N"))</f>
         <v/>
@@ -8622,22 +8384,22 @@
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (news 25, mapillary 35); map shows 25</t>
         </is>
       </c>
       <c r="Y80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>67</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OCN-B1-002</t>
+          <t>OCN-B1-001</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -8647,22 +8409,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>Pacific Coast Highway</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Morse Street</t>
+          <t>Kelly Street</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pacific Coast Highway</t>
+          <t>Vista Way</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>436403815</t>
+          <t>1029525635</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -8670,7 +8432,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -8680,12 +8442,12 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.178201,-117.364689&amp;heading=145</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.172694,-117.360051&amp;heading=145</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.178201,-117.364689</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.172694,-117.360051</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -8699,21 +8461,9 @@
       </c>
       <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Coast Highway (Wisconsin Ave - south city limit)</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>https://gocodebook.com/library/us/ca/oceanside/oceanside-traffic-code-1/article-xiv-special-speed-zones</t>
-        </is>
-      </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
       <c r="V81">
         <f>IF(OR(L81="",S81=""),"",IF(VALUE(L81)=VALUE(S81),"Y","N"))</f>
         <v/>
@@ -8724,7 +8474,7 @@
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 30)</t>
+          <t>sources disagree: sources disagree (osm 30, mapillary 35); map shows 35</t>
         </is>
       </c>
       <c r="Y81" t="n">
@@ -8732,14 +8482,14 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>189</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OCN-B1-003</t>
+          <t>OCN-B1-002</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -8749,41 +8499,41 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wisconsin Avenue</t>
+          <t>Pacific Coast Highway</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>South Pacific Street</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>5967620</t>
+          <t>740684253</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.186576,-117.376277&amp;heading=55</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.182823,-117.368584&amp;heading=144</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.186576,-117.376277</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=33.182823,-117.368584</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -8797,21 +8547,9 @@
       </c>
       <c r="Q82" t="inlineStr"/>
       <c r="R82" t="inlineStr"/>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
-        <is>
-          <t>Oceanside Traffic Code Art. XIV 18: Wisconsin Avenue (South Coast Highway - South Pacific Street) posted 25</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
-        <is>
-          <t>https://gocodebook.com/library/us/ca/oceanside/oceanside-traffic-code-1/article-xiv-special-speed-zones</t>
-        </is>
-      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
       <c r="V82">
         <f>IF(OR(L82="",S82=""),"",IF(VALUE(L82)=VALUE(S82),"Y","N"))</f>
         <v/>
@@ -8822,70 +8560,70 @@
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>sources disagree: sources disagree (osm 30, mapillary 35); map shows 35</t>
         </is>
       </c>
       <c r="Y82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>121</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>OCN-B1-004</t>
+          <t>PBC-B1-001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Oceanside</t>
+          <t>Pacific Beach / Mission Beach</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Wisconsin Avenue</t>
+          <t>Grand Avenue</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>South Myers Street</t>
+          <t>Ingraham Street</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>South Tait Street</t>
+          <t>Haines Street</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>617084571</t>
+          <t>436316485</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.187265,-117.375345&amp;heading=37</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.797830,-117.240786&amp;heading=255</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.187265,-117.375345</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.797830,-117.240786</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -8899,21 +8637,9 @@
       </c>
       <c r="Q83" t="inlineStr"/>
       <c r="R83" t="inlineStr"/>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
-        <is>
-          <t>Oceanside Traffic Code Art. XIV 18: Wisconsin Avenue (South Coast Highway - South Pacific Street) posted 25</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
-        <is>
-          <t>https://gocodebook.com/library/us/ca/oceanside/oceanside-traffic-code-1/article-xiv-special-speed-zones</t>
-        </is>
-      </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
       <c r="V83">
         <f>IF(OR(L83="",S83=""),"",IF(VALUE(L83)=VALUE(S83),"Y","N"))</f>
         <v/>
@@ -8924,47 +8650,47 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 45, mapillary 35, mapillary 35); map shows 35</t>
         </is>
       </c>
       <c r="Y83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>137</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>OCN-B1-005</t>
+          <t>PBC-B1-002</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Oceanside</t>
+          <t>Pacific Beach / Mission Beach</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Wisconsin Avenue</t>
+          <t>La Jolla Boulevard</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>South Myers Street</t>
+          <t>Opal Street</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pacific Coast Highway</t>
+          <t>Loring Street</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>617084573</t>
+          <t>436401815</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -8982,12 +8708,12 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=33.188260,-117.373842&amp;heading=54</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.804989,-117.258585&amp;heading=148</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=33.188260,-117.373842</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.804989,-117.258585</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -9008,12 +8734,12 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>Oceanside Traffic Code Art. XIV 18: Wisconsin Avenue (South Coast Highway - South Pacific Street) posted 25</t>
+          <t>San Diego R-316675 Table 7, posted: La Jolla Bl (Loring St - Colima St)</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
         <is>
-          <t>https://gocodebook.com/library/us/ca/oceanside/oceanside-traffic-code-1/article-xiv-special-speed-zones</t>
+          <t>https://docs.sandiego.gov/council_reso_ordinance/rao2026/R-316675.pdf</t>
         </is>
       </c>
       <c r="V84">
@@ -9026,22 +8752,22 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
         </is>
       </c>
       <c r="Y84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>183</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PBC-B1-001</t>
+          <t>PBC-B1-003</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9066,7 +8792,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>436401815</t>
+          <t>436401826</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -9074,7 +8800,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>inferred</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -9084,12 +8810,12 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.804989,-117.258585&amp;heading=148</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.805392,-117.258882&amp;heading=147</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.804989,-117.258585</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.805392,-117.258882</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -9103,21 +8829,9 @@
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
-        <is>
-          <t>San Diego R-316675 Table 7, posted: La Jolla Bl (Loring St - Colima St)</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>https://docs.sandiego.gov/council_reso_ordinance/rao2026/R-316675.pdf</t>
-        </is>
-      </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
       <c r="V85">
         <f>IF(OR(L85="",S85=""),"",IF(VALUE(L85)=VALUE(S85),"Y","N"))</f>
         <v/>
@@ -9128,7 +8842,7 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: mapillary 35)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (news 25, mapillary 35); map shows 25</t>
         </is>
       </c>
       <c r="Y85" t="n">
@@ -9136,14 +8850,14 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>48</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PBC-B1-002</t>
+          <t>PBC-B1-004</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9168,7 +8882,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>436400933</t>
+          <t>436400938</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -9186,12 +8900,12 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.769886,-117.251031&amp;heading=178</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.771256,-117.251118&amp;heading=172</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.769886,-117.251031</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.771256,-117.251118</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -9230,7 +8944,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: mapillary 30)</t>
         </is>
       </c>
       <c r="Y86" t="n">
@@ -9238,14 +8952,14 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>149</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PBC-B1-003</t>
+          <t>PBC-B1-005</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9260,17 +8974,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>San Fernando Place</t>
+          <t>West Mission Bay Drive</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>West Mission Bay Drive</t>
+          <t>Santa Barbara Place</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>436400936</t>
+          <t>1019974701</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -9288,12 +9002,12 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.770753,-117.250884&amp;heading=355</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.773130,-117.251355&amp;heading=350</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.770753,-117.250884</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.773130,-117.251355</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -9332,7 +9046,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 25 mph (OSM/imagery: mapillary 30)</t>
         </is>
       </c>
       <c r="Y87" t="n">
@@ -9340,14 +9054,14 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>184</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PBC-B1-004</t>
+          <t>PBC-B1-006</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9362,17 +9076,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Ventura Place</t>
+          <t>Diamond Street</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>San Fernando Place</t>
+          <t>Missouri Street</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>436400938</t>
+          <t>436608595</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -9380,7 +9094,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>inferred</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -9390,12 +9104,12 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.771256,-117.251118&amp;heading=172</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.799836,-117.256495&amp;heading=346</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.771256,-117.251118</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.799836,-117.256495</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -9409,21 +9123,9 @@
       </c>
       <c r="Q88" t="inlineStr"/>
       <c r="R88" t="inlineStr"/>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>San Diego R-316675 Table 7, posted: Mission Bl (San Fernando Pl - Santa Clara Pl)</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>https://docs.sandiego.gov/council_reso_ordinance/rao2026/R-316675.pdf</t>
-        </is>
-      </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
       <c r="V88">
         <f>IF(OR(L88="",S88=""),"",IF(VALUE(L88)=VALUE(S88),"Y","N"))</f>
         <v/>
@@ -9434,7 +9136,7 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: mapillary 30)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (news 25, mapillary 30); map shows 25</t>
         </is>
       </c>
       <c r="Y88" t="n">
@@ -9442,14 +9144,14 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>52</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PBC-B1-005</t>
+          <t>PBC-B1-007</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9464,17 +9166,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>San Fernando Place</t>
+          <t>Diamond Street</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>West Mission Bay Drive</t>
+          <t>Missouri Street</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>436400932</t>
+          <t>436608578</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -9482,7 +9184,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>inferred</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -9492,12 +9194,12 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.771870,-117.251098&amp;heading=351</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.800311,-117.256640&amp;heading=346</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.771870,-117.251098</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.800311,-117.256640</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -9511,21 +9213,9 @@
       </c>
       <c r="Q89" t="inlineStr"/>
       <c r="R89" t="inlineStr"/>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>San Diego R-316675 Table 7, posted: Mission Bl (San Fernando Pl - Santa Clara Pl)</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>https://docs.sandiego.gov/council_reso_ordinance/rao2026/R-316675.pdf</t>
-        </is>
-      </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
       <c r="V89">
         <f>IF(OR(L89="",S89=""),"",IF(VALUE(L89)=VALUE(S89),"Y","N"))</f>
         <v/>
@@ -9536,7 +9226,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (news 25, mapillary 30); map shows 25</t>
         </is>
       </c>
       <c r="Y89" t="n">
@@ -9544,14 +9234,14 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PBC-B1-006</t>
+          <t>PBC-B1-008</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9566,17 +9256,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>West Mission Bay Drive</t>
+          <t>Beryl Street</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Santa Barbara Place</t>
+          <t>Wilbur Avenue</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1019974701</t>
+          <t>436608589</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -9584,7 +9274,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>inferred</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -9594,12 +9284,12 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.773130,-117.251355&amp;heading=350</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.803558,-117.257637&amp;heading=345</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.773130,-117.251355</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.803558,-117.257637</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -9613,21 +9303,9 @@
       </c>
       <c r="Q90" t="inlineStr"/>
       <c r="R90" t="inlineStr"/>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>San Diego R-316675 Table 7, posted: Mission Bl (San Fernando Pl - Santa Clara Pl)</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>https://docs.sandiego.gov/council_reso_ordinance/rao2026/R-316675.pdf</t>
-        </is>
-      </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
       <c r="V90">
         <f>IF(OR(L90="",S90=""),"",IF(VALUE(L90)=VALUE(S90),"Y","N"))</f>
         <v/>
@@ -9638,7 +9316,7 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 25 mph (OSM/imagery: mapillary 30)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (news 25, mapillary 30); map shows 25</t>
         </is>
       </c>
       <c r="Y90" t="n">
@@ -9646,14 +9324,14 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>90</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PBC-B1-007</t>
+          <t>PBC-B1-009</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9668,17 +9346,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Santa Barbara Place</t>
+          <t>Wilbur Avenue</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ventura Place</t>
+          <t>La Jolla Boulevard</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>436400724</t>
+          <t>436608590</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -9686,7 +9364,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>inferred</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -9696,12 +9374,12 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.773380,-117.251493&amp;heading=168</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.804505,-117.257923&amp;heading=345</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.773380,-117.251493</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.804505,-117.257923</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -9715,21 +9393,9 @@
       </c>
       <c r="Q91" t="inlineStr"/>
       <c r="R91" t="inlineStr"/>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>San Diego R-316675 Table 7, posted: Mission Bl (San Fernando Pl - Santa Clara Pl)</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
-        <is>
-          <t>https://docs.sandiego.gov/council_reso_ordinance/rao2026/R-316675.pdf</t>
-        </is>
-      </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
       <c r="V91">
         <f>IF(OR(L91="",S91=""),"",IF(VALUE(L91)=VALUE(S91),"Y","N"))</f>
         <v/>
@@ -9740,7 +9406,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (news 25, mapillary 30); map shows 25</t>
         </is>
       </c>
       <c r="Y91" t="n">
@@ -9748,43 +9414,43 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PBC-B1-008</t>
+          <t>SOL-B1-001</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Pacific Beach / Mission Beach</t>
+          <t>Solana Beach</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Mission Boulevard</t>
+          <t>Lomas Santa Fe Drive</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>San Luis Obispo Place</t>
+          <t>Plaza Street</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Santa Barbara Place</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>436400725</t>
+          <t>26328612</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -9793,17 +9459,17 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.775441,-117.252172&amp;heading=164</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.991875,-117.271607&amp;heading=78</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.775441,-117.252172</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.991875,-117.271607</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -9819,17 +9485,17 @@
       <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>San Diego R-316675 Table 7, posted: Mission Bl (San Fernando Pl - Santa Clara Pl)</t>
+          <t>Lomas Santa Fe Dr (Hwy 101 - Stevens Ave)</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
         <is>
-          <t>https://docs.sandiego.gov/council_reso_ordinance/rao2026/R-316675.pdf</t>
+          <t>https://cityofsolanabeach.ca.gov/sites/default/files/Solana%20Beach/Meetings/City%20Council/2023/07-12-23/07-12-23%20Reg/A.3.%20Report%20-%2007-12-23%20-%20O.pdf</t>
         </is>
       </c>
       <c r="V92">
@@ -9842,7 +9508,7 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 35 mph (OSM/imagery: osm 50)</t>
         </is>
       </c>
       <c r="Y92" t="n">
@@ -9850,43 +9516,43 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>13</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PBC-B1-009</t>
+          <t>SOL-B1-002</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pacific Beach / Mission Beach</t>
+          <t>Solana Beach</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Mission Boulevard</t>
+          <t>Lomas Santa Fe Drive</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>San Luis Obispo Place</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tom Lane</t>
+          <t>North Cedros Avenue</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1025161103</t>
+          <t>436403292</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -9895,17 +9561,17 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.777001,-117.252478&amp;heading=351</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.991894,-117.271507&amp;heading=76</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.777001,-117.252478</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.991894,-117.271507</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -9921,17 +9587,17 @@
       <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>San Diego R-316675 Table 7, posted: Mission Bl (San Fernando Pl - Santa Clara Pl)</t>
+          <t>Lomas Santa Fe Dr (Hwy 101 - Stevens Ave)</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>https://docs.sandiego.gov/council_reso_ordinance/rao2026/R-316675.pdf</t>
+          <t>https://cityofsolanabeach.ca.gov/sites/default/files/Solana%20Beach/Meetings/City%20Council/2023/07-12-23/07-12-23%20Reg/A.3.%20Report%20-%2007-12-23%20-%20O.pdf</t>
         </is>
       </c>
       <c r="V93">
@@ -9944,7 +9610,7 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 35 mph (OSM/imagery: osm 50)</t>
         </is>
       </c>
       <c r="Y93" t="n">
@@ -9952,43 +9618,43 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>17</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PBC-B1-010</t>
+          <t>SOL-B1-003</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Pacific Beach / Mission Beach</t>
+          <t>Solana Beach</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Mission Boulevard</t>
+          <t>Lomas Santa Fe Drive</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>El Carmel Place</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>San Luis Obispo Place</t>
+          <t>North Cedros Avenue</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>436400713</t>
+          <t>32677195</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -9997,17 +9663,17 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.777257,-117.252606&amp;heading=174</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.991939,-117.271241&amp;heading=80</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.777257,-117.252606</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.991939,-117.271241</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -10023,17 +9689,17 @@
       <c r="R94" t="inlineStr"/>
       <c r="S94" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>San Diego R-316675 Table 7, posted: Mission Bl (San Fernando Pl - Santa Clara Pl)</t>
+          <t>Lomas Santa Fe Dr (Hwy 101 - Stevens Ave)</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
         <is>
-          <t>https://docs.sandiego.gov/council_reso_ordinance/rao2026/R-316675.pdf</t>
+          <t>https://cityofsolanabeach.ca.gov/sites/default/files/Solana%20Beach/Meetings/City%20Council/2023/07-12-23/07-12-23%20Reg/A.3.%20Report%20-%2007-12-23%20-%20O.pdf</t>
         </is>
       </c>
       <c r="V94">
@@ -10046,7 +9712,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 35 mph (OSM/imagery: osm 50)</t>
         </is>
       </c>
       <c r="Y94" t="n">
@@ -10054,43 +9720,43 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PBC-B1-011</t>
+          <t>SOL-B1-004</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pacific Beach / Mission Beach</t>
+          <t>Solana Beach</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Mission Boulevard</t>
+          <t>Lomas Santa Fe Drive</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>San Juan Place</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>San Luis Obispo Place</t>
+          <t>North Cedros Avenue</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1025161220</t>
+          <t>436403302</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -10099,17 +9765,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.778356,-117.252655&amp;heading=181</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.991962,-117.271128&amp;heading=76</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.778356,-117.252655</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.991962,-117.271128</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -10125,17 +9791,17 @@
       <c r="R95" t="inlineStr"/>
       <c r="S95" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>San Diego R-316675 Table 7, posted: Mission Bl (San Fernando Pl - Santa Clara Pl)</t>
+          <t>Lomas Santa Fe Dr (Hwy 101 - Stevens Ave)</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
         <is>
-          <t>https://docs.sandiego.gov/council_reso_ordinance/rao2026/R-316675.pdf</t>
+          <t>https://cityofsolanabeach.ca.gov/sites/default/files/Solana%20Beach/Meetings/City%20Council/2023/07-12-23/07-12-23%20Reg/A.3.%20Report%20-%2007-12-23%20-%20O.pdf</t>
         </is>
       </c>
       <c r="V95">
@@ -10148,7 +9814,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 35 mph (OSM/imagery: osm 50)</t>
         </is>
       </c>
       <c r="Y95" t="n">
@@ -10156,43 +9822,43 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>11</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PBC-B1-012</t>
+          <t>SOL-B1-005</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pacific Beach / Mission Beach</t>
+          <t>Solana Beach</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Mission Boulevard</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>San Juan Place</t>
+          <t>Lomas Santa Fe Drive</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>El Carmel Place</t>
+          <t>Dahlia Drive</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1025161219</t>
+          <t>168702015</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -10201,17 +9867,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.779334,-117.252623&amp;heading=182</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.989713,-117.271229&amp;heading=169</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.779334,-117.252623</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.989713,-117.271229</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -10227,17 +9893,17 @@
       <c r="R96" t="inlineStr"/>
       <c r="S96" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>San Diego R-316675 Table 7, posted: Mission Bl (San Fernando Pl - Santa Clara Pl)</t>
+          <t>Highway 101 (S Coast Hwy / Camino del Mar) (North City Limit - Dahlia Dr)</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>https://docs.sandiego.gov/council_reso_ordinance/rao2026/R-316675.pdf</t>
+          <t>https://cityofsolanabeach.ca.gov/sites/default/files/Solana%20Beach/Meetings/City%20Council/2023/07-12-23/07-12-23%20Reg/A.3.%20Report%20-%2007-12-23%20-%20O.pdf</t>
         </is>
       </c>
       <c r="V96">
@@ -10250,7 +9916,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; map uses the official 35 mph (OSM/imagery: osm 45)</t>
         </is>
       </c>
       <c r="Y96" t="n">
@@ -10258,62 +9924,62 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>501</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PBC-B1-013</t>
+          <t>SOL-B1-006</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Pacific Beach / Mission Beach</t>
+          <t>Solana Beach</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Mission Boulevard</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Santa Clara Place</t>
+          <t>Estrella Street</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>San Juan Place</t>
+          <t>Lomas Santa Fe Drive</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1187547621</t>
+          <t>436403289</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>cart+LSV</t>
+          <t>LSV</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.781190,-117.252556&amp;heading=182</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.992012,-117.271783&amp;heading=169</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.781190,-117.252556</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.992012,-117.271783</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -10327,21 +9993,9 @@
       </c>
       <c r="Q97" t="inlineStr"/>
       <c r="R97" t="inlineStr"/>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="T97" t="inlineStr">
-        <is>
-          <t>San Diego R-316675 Table 7, posted: Mission Bl (San Fernando Pl - Santa Clara Pl)</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>https://docs.sandiego.gov/council_reso_ordinance/rao2026/R-316675.pdf</t>
-        </is>
-      </c>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
       <c r="V97">
         <f>IF(OR(L97="",S97=""),"",IF(VALUE(L97)=VALUE(S97),"Y","N"))</f>
         <v/>
@@ -10352,7 +10006,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>one official source; most-used arterial</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 45, streetview 30); map shows 30</t>
         </is>
       </c>
       <c r="Y97" t="n">
@@ -10360,14 +10014,14 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>123</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SOL-B1-001</t>
+          <t>SOL-B1-007</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10377,30 +10031,30 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
+          <t>South Coast Highway</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Estrella Street</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>Lomas Santa Fe Drive</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Plaza Street</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>South Coast Highway</t>
-        </is>
-      </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>26328612</t>
+          <t>780284924</t>
         </is>
       </c>
       <c r="G98" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -10410,12 +10064,12 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.991875,-117.271607&amp;heading=78</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.993363,-117.272100&amp;heading=169</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.991875,-117.271607</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.993363,-117.272100</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -10429,21 +10083,9 @@
       </c>
       <c r="Q98" t="inlineStr"/>
       <c r="R98" t="inlineStr"/>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T98" t="inlineStr">
-        <is>
-          <t>Lomas Santa Fe Dr (Hwy 101 - Stevens Ave)</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>https://cityofsolanabeach.ca.gov/sites/default/files/Solana%20Beach/Meetings/City%20Council/2023/07-12-23/07-12-23%20Reg/A.3.%20Report%20-%2007-12-23%20-%20O.pdf</t>
-        </is>
-      </c>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
       <c r="V98">
         <f>IF(OR(L98="",S98=""),"",IF(VALUE(L98)=VALUE(S98),"Y","N"))</f>
         <v/>
@@ -10454,7 +10096,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 50)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 45, streetview 30); map shows 30</t>
         </is>
       </c>
       <c r="Y98" t="n">
@@ -10462,14 +10104,14 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>207</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SOL-B1-002</t>
+          <t>SOL-B1-008</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10479,30 +10121,30 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Lomas Santa Fe Drive</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>West Cliff Street</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>North Cedros Avenue</t>
+          <t>Estrella Street</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>436403292</t>
+          <t>224931099</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -10512,12 +10154,12 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.991894,-117.271507&amp;heading=76</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.995267,-117.272660&amp;heading=160</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.991894,-117.271507</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.995267,-117.272660</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -10531,21 +10173,9 @@
       </c>
       <c r="Q99" t="inlineStr"/>
       <c r="R99" t="inlineStr"/>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T99" t="inlineStr">
-        <is>
-          <t>Lomas Santa Fe Dr (Hwy 101 - Stevens Ave)</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>https://cityofsolanabeach.ca.gov/sites/default/files/Solana%20Beach/Meetings/City%20Council/2023/07-12-23/07-12-23%20Reg/A.3.%20Report%20-%2007-12-23%20-%20O.pdf</t>
-        </is>
-      </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
       <c r="V99">
         <f>IF(OR(L99="",S99=""),"",IF(VALUE(L99)=VALUE(S99),"Y","N"))</f>
         <v/>
@@ -10556,7 +10186,7 @@
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 50)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 45, streetview 30, mapillary 35); map shows 30</t>
         </is>
       </c>
       <c r="Y99" t="n">
@@ -10564,14 +10194,14 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>239</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SOL-B1-003</t>
+          <t>SOL-B1-009</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10581,30 +10211,30 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lomas Santa Fe Drive</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>Cardiff State Beach</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>North Cedros Avenue</t>
+          <t>Ocean Street</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>32677195</t>
+          <t>1268448802</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -10614,12 +10244,12 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.991939,-117.271241&amp;heading=80</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.999524,-117.274795&amp;heading=155</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.991939,-117.271241</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.999524,-117.274795</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -10633,21 +10263,9 @@
       </c>
       <c r="Q100" t="inlineStr"/>
       <c r="R100" t="inlineStr"/>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr">
-        <is>
-          <t>Lomas Santa Fe Dr (Hwy 101 - Stevens Ave)</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>https://cityofsolanabeach.ca.gov/sites/default/files/Solana%20Beach/Meetings/City%20Council/2023/07-12-23/07-12-23%20Reg/A.3.%20Report%20-%2007-12-23%20-%20O.pdf</t>
-        </is>
-      </c>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
       <c r="V100">
         <f>IF(OR(L100="",S100=""),"",IF(VALUE(L100)=VALUE(S100),"Y","N"))</f>
         <v/>
@@ -10658,7 +10276,7 @@
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 50)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 45, streetview 30); map shows 30</t>
         </is>
       </c>
       <c r="Y100" t="n">
@@ -10666,14 +10284,14 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>SOL-B1-004</t>
+          <t>SOL-B1-010</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10683,30 +10301,30 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lomas Santa Fe Drive</t>
+          <t>South Coast Highway</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>South Coast Highway</t>
+          <t>Cardiff State Beach</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>North Cedros Avenue</t>
+          <t>Ocean Street</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>436403302</t>
+          <t>34092347</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>city/county</t>
+          <t>tag</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10716,12 +10334,12 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.991962,-117.271128&amp;heading=76</t>
+          <t>https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=32.999686,-117.274887&amp;heading=155</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=32.991962,-117.271128</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=32.999686,-117.274887</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -10735,21 +10353,9 @@
       </c>
       <c r="Q101" t="inlineStr"/>
       <c r="R101" t="inlineStr"/>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="T101" t="inlineStr">
-        <is>
-          <t>Lomas Santa Fe Dr (Hwy 101 - Stevens Ave)</t>
-        </is>
-      </c>
-      <c r="U101" t="inlineStr">
-        <is>
-          <t>https://cityofsolanabeach.ca.gov/sites/default/files/Solana%20Beach/Meetings/City%20Council/2023/07-12-23/07-12-23%20Reg/A.3.%20Report%20-%2007-12-23%20-%20O.pdf</t>
-        </is>
-      </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
       <c r="V101">
         <f>IF(OR(L101="",S101=""),"",IF(VALUE(L101)=VALUE(S101),"Y","N"))</f>
         <v/>
@@ -10760,7 +10366,7 @@
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>sources disagree: map uses the official 35 mph (OSM/imagery: osm 50)</t>
+          <t>SAFETY: map allows more than a sign/OSM reading; sources disagree (osm 45, streetview 30); map shows 30</t>
         </is>
       </c>
       <c r="Y101" t="n">
@@ -10768,7 +10374,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
     </row>
